--- a/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est au jardin avec maman. Une petite plante a soif. Ses feuilles sont molles. Maman dit : elle a besoin d'eau. Elle a besoin de lumière. Jules prend l'arrosoir avec maman. Ils versent un peu d'eau. La terre devient sombre. Maman pose le pot près de la fenêtre. La lumière arrive. Jules touche une feuille. C'est doux. Maman dit : on arrose avec un adulte.</t>
+          <t>Jules est au jardin avec maman. Une petite plante a soif. Ses feuilles sont molles. Elle a besoin d'eau. Elle a besoin de lumière. Jules prend l'arrosoir avec maman. Ils versent un peu d'eau. La terre devient sombre. Maman pose le pot près de la fenêtre. La lumière arrive. Jules touche une feuille. C'est doux. On arrose avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est au jardin avec maman. Une petite plante a soif. Ses feuilles sont molles.
+maman|Elle a besoin d'eau. Elle a besoin de lumière.
+narrateur|Jules prend l'arrosoir avec maman. Ils versent un peu d'eau. La terre devient sombre. Maman pose le pot près de la fenêtre. La lumière arrive. Jules touche une feuille. C'est doux.
+maman|On arrose avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La plante a soif. Que fait Jules avec maman ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a versé l'eau. La lumière est là. Maman, l'adulte, était avec lui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range l'arrosoir. La plante tient droit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 maman|On arrose avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|La plante a soif. Que fait Jules avec maman ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Jules a versé l'eau. La lumière est là. Maman, l'adulte, était avec lui.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Jules range l'arrosoir. La plante tient droit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L'arrosoir de Jules</t>
+          <t>L'odeur des pâtes d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut l'odeur du basilic sur les pâtes du soir. Le basilic a soif. Trop d'eau, la soucoupe déborde. Ils vident. Une feuille se redresse.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est au jardin avec maman. Une petite plante a soif. Ses feuilles sont molles. Elle a besoin d'eau. Elle a besoin de lumière. Jules prend l'arrosoir avec maman. Ils versent un peu d'eau. La terre devient sombre. Maman pose le pot près de la fenêtre. La lumière arrive. Jules touche une feuille. C'est doux. On arrose avec un adulte.</t>
+          <t>Le rebord de la fenêtre est tiède. Un carré de soleil pose sur le pot. Ça sent la sauce tomate. La casserole chante tout bas. Les pâtes du soir attendent. Amir vit ici, avec maman. Tu as vu le basilic ? Il est tout mou. Les feuilles pendent, un peu. La terre est claire, presque grise. Je veux son odeur. Sur les pâtes du soir. Il a soif, alors. Tu viens près du pot ? En ce moment, Amir s'approche. Il touche une feuille. La feuille est chaude et molle. Elle est triste. Elle a besoin d'eau. Un peu, pas trop. L'arrosoir bleu attend près de l'évier. Amir le tire par l'anse. L'eau cloche dedans. C'est lourd. On verse ensemble ? Oui, maman. Amir penche l'arrosoir. Maman tient l'anse aussi. L'eau tombe sur la terre. La terre devient sombre. Elle boit ! Oui. Tout doux. Une goutte reste sur une feuille. Elle brille, toute ronde. Une perle. On verra si c'est assez.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules est au jardin avec maman. Une petite plante a soif. Ses feuilles sont molles. Maman dit : elle a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Jules prend l'arrosoir avec maman. Ils versent un peu d'eau. La terre devient sombre. Maman pose le pot près de la fenêtre. La lumière arrive. Jules touche une feuille. C'est doux. Maman dit : on arrose avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rebord de la fenêtre est tiède. Un carré de soleil pose sur le pot. Ça sent la sauce tomate. La casserole chante tout bas. Les pâtes du soir attendent. Amir vit ici, avec maman. Tu as vu le basilic ? Il est tout mou. Les feuilles pendent, un peu. La terre est claire, presque grise. Je veux son odeur. Sur les pâtes du soir. Il a soif, alors. Tu viens près du pot ? En ce moment, Amir s'approche. Il touche une feuille. La feuille est chaude et molle. Elle est triste. Elle a besoin d'eau. Un peu, pas trop. L'arrosoir bleu attend près de l'évier. Amir le tire par l'anse. L'eau cloche dedans. C'est lourd. On verse ensemble ? Oui, maman. Amir penche l'arrosoir. Maman tient l'anse aussi. L'eau tombe sur la terre. La terre devient sombre. Elle boit ! Oui. Tout doux. Une goutte reste sur une feuille. Elle brille, toute ronde. Une perle. On verra si c'est assez.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules est au jardin avec maman. Une petite plante a soif. Ses feuilles sont molles.
-maman|Elle a besoin d'eau. Elle a besoin de lumière.
-narrateur|Jules prend l'arrosoir avec maman. Ils versent un peu d'eau. La terre devient sombre. Maman pose le pot près de la fenêtre. La lumière arrive. Jules touche une feuille. C'est doux.
-maman|On arrose avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le rebord de la fenêtre est tiède.
+narrateur|Un carré de soleil pose sur le pot.
+narrateur|Ça sent la sauce tomate.
+narrateur|La casserole chante tout bas.
+narrateur|Les pâtes du soir attendent.
+narrateur|Amir vit ici, avec maman.
+maman|Tu as vu le basilic ?
+enfant-m|Il est tout mou.
+narrateur|Les feuilles pendent, un peu.
+narrateur|La terre est claire, presque grise.
+enfant-m|Je veux son odeur.
+enfant-m|Sur les pâtes du soir.
+maman|Il a soif, alors.
+maman|Tu viens près du pot ?
+narrateur|En ce moment, Amir s'approche.
+narrateur|Il touche une feuille.
+narrateur|La feuille est chaude et molle.
+enfant-m|Elle est triste.
+maman|Elle a besoin d'eau.
+maman|Un peu, pas trop.
+narrateur|L'arrosoir bleu attend près de l'évier.
+narrateur|Amir le tire par l'anse.
+narrateur|L'eau cloche dedans.
+enfant-m|C'est lourd.
+maman|On verse ensemble ?
+enfant-m|Oui, maman.
+narrateur|Amir penche l'arrosoir.
+narrateur|Maman tient l'anse aussi.
+narrateur|L'eau tombe sur la terre.
+narrateur|La terre devient sombre.
+enfant-m|Elle boit !
+maman|Oui.
+maman|Tout doux.
+narrateur|Une goutte reste sur une feuille.
+narrateur|Elle brille, toute ronde.
+enfant-m|Une perle.
+maman|On verra si c'est assez.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1387,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La plante a soif. Que fait Jules avec maman ?</t>
+          <t>La plante a soif. Que fait Amir avec maman ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La plante a soif. Que fait Jules avec maman ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La plante a soif. Que fait Amir avec maman ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1378,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils versent de l'eau. Que fait Jules ?</t>
+          <t>Ils versent de l'eau. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1471,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1543,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La plante a soif. Que fait Jules avec maman ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La plante a soif.
+narrateur|Que fait Amir avec maman ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a versé l'eau. La lumière est là. Maman, l'adulte, était avec lui.</t>
+          <t>Amir penche encore un peu. L'eau tombe trop vite. La soucoupe se remplit. Oh. L'eau déborde sur le bois. Trop d'eau. On vide la soucoupe ? Oui. Maman soulève le pot. Amir tient la soucoupe. Elle est froide, toute ronde. Ils versent dans l'évier. Ça fait un petit chhh. Chhh. Merci, Amir. Tu as vidé avec moi. Ils reposent le pot. Une feuille se redresse, un peu. Elle se lève ! Un peu, oui. Elle a eu trop d'eau. Puis juste assez.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules a versé l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. La lumière est là. Maman, l'adulte, était avec lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir penche encore un peu. L'eau tombe trop vite. La soucoupe se remplit. Oh. L'eau déborde sur le bois. Trop d'eau. On vide la soucoupe ? Oui. Maman soulève le pot. Amir tient la soucoupe. Elle est froide, toute ronde. Ils versent dans l'évier. Ça fait un petit chhh. Chhh. Merci, Amir. Tu as vidé avec moi. Ils reposent le pot. Une feuille se redresse, un peu. Elle se lève ! Un peu, oui. Elle a eu trop d'eau. Puis juste assez.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1588,14 +1632,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1715,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules a versé l'eau. La lumière est là. Maman, l'adulte, était avec lui.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir penche encore un peu.
+narrateur|L'eau tombe trop vite.
+narrateur|La soucoupe se remplit.
+enfant-m|Oh.
+narrateur|L'eau déborde sur le bois.
+maman|Trop d'eau.
+maman|On vide la soucoupe ?
+enfant-m|Oui.
+narrateur|Maman soulève le pot.
+narrateur|Amir tient la soucoupe.
+narrateur|Elle est froide, toute ronde.
+narrateur|Ils versent dans l'évier.
+narrateur|Ça fait un petit chhh.
+enfant-m|Chhh.
+maman|Merci, Amir.
+maman|Tu as vidé avec moi.
+narrateur|Ils reposent le pot.
+narrateur|Une feuille se redresse, un peu.
+enfant-m|Elle se lève !
+maman|Un peu, oui.
+maman|Elle a eu trop d'eau.
+maman|Puis juste assez.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Jules range l'arrosoir. La plante tient droit.</t>
+          <t>Le soir arrive dans la cuisine. La vapeur des pâtes est chaude. On prend une feuille ? Une seule, la plus grande. Amir pince la tige. La feuille sent fort, tout de suite. Ça pique le nez ! C'est le basilic. Tu la poses sur les pâtes ? Oui. La feuille tombe dans la vapeur. Elle devient brillante. La sauce sent le vert. Tu as aidé le basilic. Merci. Il a bu. Une goutte sèche sur le bois. Le pot reste près de la vitre. Tu as fini ta fourchette ? Presque. Amir reprend une pâte. Elle est chaude, un peu glissante. Encore l'odeur. Oui. Le basilic est dans l'assiette.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules range l'arrosoir. La plante tient droit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le soir arrive dans la cuisine. La vapeur des pâtes est chaude. On prend une feuille ? Une seule, la plus grande. Amir pince la tige. La feuille sent fort, tout de suite. Ça pique le nez ! C'est le basilic. Tu la poses sur les pâtes ? Oui. La feuille tombe dans la vapeur. Elle devient brillante. La sauce sent le vert. Tu as aidé le basilic. Merci. Il a bu. Une goutte sèche sur le bois. Le pot reste près de la vitre. Tu as fini ta fourchette ? Presque. Amir reprend une pâte. Elle est chaude, un peu glissante. Encore l'odeur. Oui. Le basilic est dans l'assiette.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1760,14 +1824,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1899,33 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Jules range l'arrosoir. La plante tient droit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le soir arrive dans la cuisine.
+narrateur|La vapeur des pâtes est chaude.
+enfant-m|On prend une feuille ?
+maman|Une seule, la plus grande.
+narrateur|Amir pince la tige.
+narrateur|La feuille sent fort, tout de suite.
+enfant-m|Ça pique le nez !
+maman|C'est le basilic.
+maman|Tu la poses sur les pâtes ?
+enfant-m|Oui.
+narrateur|La feuille tombe dans la vapeur.
+narrateur|Elle devient brillante.
+narrateur|La sauce sent le vert.
+maman|Tu as aidé le basilic.
+maman|Merci.
+enfant-m|Il a bu.
+narrateur|Une goutte sèche sur le bois.
+narrateur|Le pot reste près de la vitre.
+maman|Tu as fini ta fourchette ?
+enfant-m|Presque.
+narrateur|Amir reprend une pâte.
+narrateur|Elle est chaude, un peu glissante.
+enfant-m|Encore l'odeur.
+maman|Oui.
+maman|Le basilic est dans l'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Amir souffle sur sa fourchette. La vapeur sent le basilic. Les pâtes du soir. Oui. Avec l'odeur que tu voulais. La vapeur des pâtes sent le basilic.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir souffle sur sa fourchette. La vapeur sent le basilic. Les pâtes du soir. Oui. Avec l'odeur que tu voulais. La vapeur des pâtes sent le basilic.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1924,14 +2011,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,10 +2090,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Amir souffle sur sa fourchette.
+narrateur|La vapeur sent le basilic.
+enfant-m|Les pâtes du soir.
+maman|Oui.
+maman|Avec l'odeur que tu voulais.
+narrateur|La vapeur des pâtes sent le basilic.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>cuisine, basilic à la fenêtre</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
